--- a/informes_data/Segunda FEB/2025-26/Regular_Season/aggregate_individual/AGG_IND_CASTILLO DE GORRAIZ VALLE DE EGÜES.xlsx
+++ b/informes_data/Segunda FEB/2025-26/Regular_Season/aggregate_individual/AGG_IND_CASTILLO DE GORRAIZ VALLE DE EGÜES.xlsx
@@ -565,13 +565,13 @@
         <v>7</v>
       </c>
       <c r="D2" t="n">
-        <v>14.4255</v>
+        <v>12.0772</v>
       </c>
       <c r="E2" t="n">
-        <v>7.013100000000001</v>
+        <v>5.6665</v>
       </c>
       <c r="F2" t="n">
-        <v>7.4127</v>
+        <v>6.410299999999999</v>
       </c>
       <c r="G2" t="n">
         <v>4.0895</v>
@@ -610,13 +610,13 @@
         <v>16.0252</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.02669999999999995</v>
+        <v>-2.3753</v>
       </c>
       <c r="T2" t="n">
-        <v>-1.1488</v>
+        <v>-2.495</v>
       </c>
       <c r="U2" t="n">
-        <v>1.1222</v>
+        <v>0.1200000000000001</v>
       </c>
       <c r="V2" t="n">
         <v>6.824800000000001</v>
@@ -643,13 +643,13 @@
         <v>3</v>
       </c>
       <c r="D3" t="n">
-        <v>1.4194</v>
+        <v>1.5661</v>
       </c>
       <c r="E3" t="n">
         <v>1.7095</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.2901000000000001</v>
+        <v>-0.1433000000000001</v>
       </c>
       <c r="G3" t="n">
         <v>0.2193</v>
@@ -688,13 +688,13 @@
         <v>0.2081</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.1756</v>
+        <v>-0.0287</v>
       </c>
       <c r="T3" t="n">
         <v>-0.1305</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.04509999999999999</v>
+        <v>0.1018</v>
       </c>
       <c r="V3" t="n">
         <v>1.1675</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>P. PIEKUS</t>
+          <t>C. ZIZIC</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -718,76 +718,76 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="D4" t="n">
-        <v>1.1992</v>
+        <v>-0.2483</v>
       </c>
       <c r="E4" t="n">
-        <v>7.2719</v>
+        <v>1.8986</v>
       </c>
       <c r="F4" t="n">
-        <v>-6.0727</v>
+        <v>-2.147</v>
       </c>
       <c r="G4" t="n">
-        <v>-3.6927</v>
+        <v>1.6329</v>
       </c>
       <c r="H4" t="n">
-        <v>-1.3048</v>
+        <v>1.0834</v>
       </c>
       <c r="I4" t="n">
-        <v>-2.3879</v>
+        <v>0.5495000000000001</v>
       </c>
       <c r="J4" t="n">
-        <v>4.0603</v>
+        <v>5.5566</v>
       </c>
       <c r="K4" t="n">
-        <v>2.2969</v>
+        <v>3.9499</v>
       </c>
       <c r="L4" t="n">
-        <v>1.7636</v>
+        <v>1.6068</v>
       </c>
       <c r="M4" t="n">
-        <v>-7.7531</v>
+        <v>-3.9238</v>
       </c>
       <c r="N4" t="n">
-        <v>-3.6018</v>
+        <v>-2.8665</v>
       </c>
       <c r="O4" t="n">
-        <v>-4.1514</v>
+        <v>-1.0572</v>
       </c>
       <c r="P4" t="n">
-        <v>1.6649</v>
+        <v>-0.6242999999999999</v>
       </c>
       <c r="Q4" t="n">
-        <v>-5.202999999999999</v>
+        <v>-4.1624</v>
       </c>
       <c r="R4" t="n">
-        <v>6.867900000000001</v>
+        <v>3.538</v>
       </c>
       <c r="S4" t="n">
-        <v>8.502000000000001</v>
+        <v>0.3634999999999999</v>
       </c>
       <c r="T4" t="n">
-        <v>8.6798</v>
+        <v>0.6283000000000001</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.1778</v>
+        <v>-0.2647999999999999</v>
       </c>
       <c r="V4" t="n">
-        <v>-5.2752</v>
+        <v>-1.6204</v>
       </c>
       <c r="W4" t="n">
-        <v>-0.2654000000000001</v>
+        <v>-0.1238</v>
       </c>
       <c r="X4" t="n">
-        <v>-5.0098</v>
+        <v>-1.4966</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>C. ZIZIC</t>
+          <t>H. ARANAZ ALVAREZ</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>4</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.04820000000000002</v>
+        <v>-0.3176</v>
       </c>
       <c r="E5" t="n">
-        <v>1.5958</v>
+        <v>-1.5127</v>
       </c>
       <c r="F5" t="n">
-        <v>-1.644</v>
+        <v>1.195</v>
       </c>
       <c r="G5" t="n">
-        <v>1.6329</v>
+        <v>0.3184</v>
       </c>
       <c r="H5" t="n">
-        <v>1.0834</v>
+        <v>-0.004199999999999982</v>
       </c>
       <c r="I5" t="n">
-        <v>0.5495000000000001</v>
+        <v>0.3225</v>
       </c>
       <c r="J5" t="n">
-        <v>5.5566</v>
+        <v>-0.3306000000000001</v>
       </c>
       <c r="K5" t="n">
-        <v>3.9499</v>
+        <v>0.3838</v>
       </c>
       <c r="L5" t="n">
-        <v>1.6068</v>
+        <v>-0.7144</v>
       </c>
       <c r="M5" t="n">
-        <v>-3.9238</v>
+        <v>0.649</v>
       </c>
       <c r="N5" t="n">
-        <v>-2.8665</v>
+        <v>-0.3879</v>
       </c>
       <c r="O5" t="n">
-        <v>-1.0572</v>
+        <v>1.0369</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.6242999999999999</v>
+        <v>-0.8325</v>
       </c>
       <c r="Q5" t="n">
-        <v>-4.1624</v>
+        <v>-1.0406</v>
       </c>
       <c r="R5" t="n">
-        <v>3.538</v>
+        <v>0.2081</v>
       </c>
       <c r="S5" t="n">
-        <v>0.5637</v>
+        <v>0.1965</v>
       </c>
       <c r="T5" t="n">
-        <v>0.3254000000000001</v>
+        <v>-0.1415</v>
       </c>
       <c r="U5" t="n">
-        <v>0.2384</v>
+        <v>0.338</v>
       </c>
       <c r="V5" t="n">
-        <v>-1.6204</v>
+        <v>0</v>
       </c>
       <c r="W5" t="n">
-        <v>-0.1238</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>-1.4966</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>H. ARANAZ ALVAREZ</t>
+          <t>I. GARBAYO ALLUE</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -874,76 +874,76 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.6889999999999999</v>
+        <v>-0.5095000000000001</v>
       </c>
       <c r="E6" t="n">
-        <v>-1.6198</v>
+        <v>-0.7099</v>
       </c>
       <c r="F6" t="n">
-        <v>0.9308000000000001</v>
+        <v>0.2005</v>
       </c>
       <c r="G6" t="n">
-        <v>0.3184</v>
+        <v>-1.7334</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.004199999999999982</v>
+        <v>-1.1064</v>
       </c>
       <c r="I6" t="n">
-        <v>0.3225</v>
+        <v>-0.627</v>
       </c>
       <c r="J6" t="n">
-        <v>-0.3306000000000001</v>
+        <v>-0.5576</v>
       </c>
       <c r="K6" t="n">
-        <v>0.3838</v>
+        <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>-0.7144</v>
+        <v>-0.5576</v>
       </c>
       <c r="M6" t="n">
-        <v>0.649</v>
+        <v>-1.1759</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.3879</v>
+        <v>-1.1064</v>
       </c>
       <c r="O6" t="n">
-        <v>1.0369</v>
+        <v>-0.06940000000000002</v>
       </c>
       <c r="P6" t="n">
-        <v>-0.8325</v>
+        <v>0.8325</v>
       </c>
       <c r="Q6" t="n">
-        <v>-1.0406</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>0.2081</v>
+        <v>0.8325</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.1749</v>
+        <v>0.3207</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.2486</v>
+        <v>-0.1523</v>
       </c>
       <c r="U6" t="n">
-        <v>0.0736</v>
+        <v>0.473</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>0.0708</v>
       </c>
       <c r="W6" t="n">
         <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>0.0708</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>I. GARBAYO ALLUE</t>
+          <t>N. DEL VAL GARCIA</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>7</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.9549</v>
+        <v>-1.4523</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.9242999999999999</v>
+        <v>-1.6822</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.03059999999999996</v>
+        <v>0.2299</v>
       </c>
       <c r="G7" t="n">
-        <v>-1.7334</v>
+        <v>-3.6516</v>
       </c>
       <c r="H7" t="n">
-        <v>-1.1064</v>
+        <v>-1.0162</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.627</v>
+        <v>-2.6354</v>
       </c>
       <c r="J7" t="n">
-        <v>-0.5576</v>
+        <v>1.2559</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>1.234</v>
       </c>
       <c r="L7" t="n">
-        <v>-0.5576</v>
+        <v>0.02179999999999993</v>
       </c>
       <c r="M7" t="n">
-        <v>-1.1759</v>
+        <v>-4.9076</v>
       </c>
       <c r="N7" t="n">
-        <v>-1.1064</v>
+        <v>-2.2502</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.06940000000000002</v>
+        <v>-2.6575</v>
       </c>
       <c r="P7" t="n">
-        <v>0.8325</v>
+        <v>2.2894</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>-5.202999999999999</v>
       </c>
       <c r="R7" t="n">
-        <v>0.8325</v>
+        <v>7.4924</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.1245</v>
+        <v>-0.5498</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.3667</v>
+        <v>0.6374</v>
       </c>
       <c r="U7" t="n">
-        <v>0.2422</v>
+        <v>-1.1871</v>
       </c>
       <c r="V7" t="n">
-        <v>0.0708</v>
+        <v>0.46</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>1.6275</v>
       </c>
       <c r="X7" t="n">
-        <v>0.0708</v>
+        <v>-1.1675</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>N. DEL VAL GARCIA</t>
+          <t>P. PIEKUS</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>7</v>
       </c>
       <c r="D8" t="n">
-        <v>-2.5934</v>
+        <v>-5.283300000000001</v>
       </c>
       <c r="E8" t="n">
-        <v>-2.4789</v>
+        <v>1.0615</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.1145</v>
+        <v>-6.345</v>
       </c>
       <c r="G8" t="n">
-        <v>-3.6516</v>
+        <v>-3.6927</v>
       </c>
       <c r="H8" t="n">
-        <v>-1.0162</v>
+        <v>-1.3048</v>
       </c>
       <c r="I8" t="n">
-        <v>-2.6354</v>
+        <v>-2.3879</v>
       </c>
       <c r="J8" t="n">
-        <v>1.2559</v>
+        <v>4.0603</v>
       </c>
       <c r="K8" t="n">
-        <v>1.234</v>
+        <v>2.2969</v>
       </c>
       <c r="L8" t="n">
-        <v>0.02179999999999993</v>
+        <v>1.7636</v>
       </c>
       <c r="M8" t="n">
-        <v>-4.9076</v>
+        <v>-7.7531</v>
       </c>
       <c r="N8" t="n">
-        <v>-2.2502</v>
+        <v>-3.6018</v>
       </c>
       <c r="O8" t="n">
-        <v>-2.6575</v>
+        <v>-4.1514</v>
       </c>
       <c r="P8" t="n">
-        <v>2.2894</v>
+        <v>1.6649</v>
       </c>
       <c r="Q8" t="n">
         <v>-5.202999999999999</v>
       </c>
       <c r="R8" t="n">
-        <v>7.4924</v>
+        <v>6.867900000000001</v>
       </c>
       <c r="S8" t="n">
-        <v>-1.6911</v>
+        <v>2.0197</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.1593000000000001</v>
+        <v>2.4695</v>
       </c>
       <c r="U8" t="n">
-        <v>-1.5315</v>
+        <v>-0.4498</v>
       </c>
       <c r="V8" t="n">
-        <v>0.46</v>
+        <v>-5.2752</v>
       </c>
       <c r="W8" t="n">
-        <v>1.6275</v>
+        <v>-0.2654000000000001</v>
       </c>
       <c r="X8" t="n">
-        <v>-1.1675</v>
+        <v>-5.0098</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A. ALFAMA AMADO</t>
+          <t>P. ELSO GONZALEZ</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1108,76 +1108,76 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D9" t="n">
-        <v>-3.225700000000001</v>
+        <v>-6.111899999999999</v>
       </c>
       <c r="E9" t="n">
-        <v>3.631699999999999</v>
+        <v>-7.1536</v>
       </c>
       <c r="F9" t="n">
-        <v>-6.857699999999999</v>
+        <v>1.0415</v>
       </c>
       <c r="G9" t="n">
-        <v>6.8829</v>
+        <v>-0.9842</v>
       </c>
       <c r="H9" t="n">
-        <v>2.585999999999999</v>
+        <v>-1.0249</v>
       </c>
       <c r="I9" t="n">
-        <v>4.2969</v>
+        <v>0.04089999999999971</v>
       </c>
       <c r="J9" t="n">
-        <v>13.1389</v>
+        <v>0.7756999999999999</v>
       </c>
       <c r="K9" t="n">
-        <v>7.3479</v>
+        <v>-0.6080000000000001</v>
       </c>
       <c r="L9" t="n">
-        <v>5.791</v>
+        <v>1.3839</v>
       </c>
       <c r="M9" t="n">
-        <v>-6.2559</v>
+        <v>-1.7598</v>
       </c>
       <c r="N9" t="n">
-        <v>-4.762</v>
+        <v>-0.4167999999999999</v>
       </c>
       <c r="O9" t="n">
-        <v>-1.4939</v>
+        <v>-1.3429</v>
       </c>
       <c r="P9" t="n">
-        <v>-5.202800000000001</v>
+        <v>-2.0811</v>
       </c>
       <c r="Q9" t="n">
-        <v>-19.355</v>
+        <v>-6.4517</v>
       </c>
       <c r="R9" t="n">
-        <v>14.1521</v>
+        <v>4.3705</v>
       </c>
       <c r="S9" t="n">
-        <v>6.3237</v>
+        <v>-1.6564</v>
       </c>
       <c r="T9" t="n">
-        <v>5.2312</v>
+        <v>-1.4776</v>
       </c>
       <c r="U9" t="n">
-        <v>1.0928</v>
+        <v>-0.1786</v>
       </c>
       <c r="V9" t="n">
-        <v>-11.2296</v>
+        <v>-1.3904</v>
       </c>
       <c r="W9" t="n">
-        <v>4.617</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>-15.8465</v>
+        <v>-1.3904</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A. GAYE</t>
+          <t>P. FERNANDEZ CHOCARRO</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1186,76 +1186,76 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>4</v>
+        <v>23</v>
       </c>
       <c r="D10" t="n">
-        <v>-7.1957</v>
+        <v>-7.8492</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.1134</v>
+        <v>6.8813</v>
       </c>
       <c r="F10" t="n">
-        <v>-7.0823</v>
+        <v>-14.7308</v>
       </c>
       <c r="G10" t="n">
-        <v>-8.405100000000001</v>
+        <v>-1.633</v>
       </c>
       <c r="H10" t="n">
-        <v>-5.5182</v>
+        <v>-5.7305</v>
       </c>
       <c r="I10" t="n">
-        <v>-2.887</v>
+        <v>4.0977</v>
       </c>
       <c r="J10" t="n">
-        <v>-2.9631</v>
+        <v>10.7233</v>
       </c>
       <c r="K10" t="n">
-        <v>-4.0604</v>
+        <v>4.9315</v>
       </c>
       <c r="L10" t="n">
-        <v>1.0973</v>
+        <v>5.7918</v>
       </c>
       <c r="M10" t="n">
-        <v>-5.4419</v>
+        <v>-12.3558</v>
       </c>
       <c r="N10" t="n">
-        <v>-1.4578</v>
+        <v>-10.6618</v>
       </c>
       <c r="O10" t="n">
-        <v>-3.9841</v>
+        <v>-1.694</v>
       </c>
       <c r="P10" t="n">
-        <v>0.8324</v>
+        <v>11.4465</v>
       </c>
       <c r="Q10" t="n">
-        <v>-2.0812</v>
+        <v>-9.989699999999999</v>
       </c>
       <c r="R10" t="n">
-        <v>2.9136</v>
+        <v>21.4361</v>
       </c>
       <c r="S10" t="n">
-        <v>1.6434</v>
+        <v>-8.057499999999999</v>
       </c>
       <c r="T10" t="n">
-        <v>1.1983</v>
+        <v>-2.1311</v>
       </c>
       <c r="U10" t="n">
-        <v>0.4451000000000001</v>
+        <v>-5.9265</v>
       </c>
       <c r="V10" t="n">
-        <v>-1.2665</v>
+        <v>-9.605699999999999</v>
       </c>
       <c r="W10" t="n">
-        <v>3.7325</v>
+        <v>8.279</v>
       </c>
       <c r="X10" t="n">
-        <v>-4.999000000000001</v>
+        <v>-17.8845</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>P. ELSO GONZALEZ</t>
+          <t>A. ALFAMA AMADO</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1264,76 +1264,76 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D11" t="n">
-        <v>-8.3643</v>
+        <v>-8.533500000000002</v>
       </c>
       <c r="E11" t="n">
-        <v>-8.118</v>
+        <v>-0.9476000000000002</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.2464999999999999</v>
+        <v>-7.5858</v>
       </c>
       <c r="G11" t="n">
-        <v>-0.9842</v>
+        <v>6.8829</v>
       </c>
       <c r="H11" t="n">
-        <v>-1.0249</v>
+        <v>2.585999999999999</v>
       </c>
       <c r="I11" t="n">
-        <v>0.04089999999999971</v>
+        <v>4.2969</v>
       </c>
       <c r="J11" t="n">
-        <v>0.7756999999999999</v>
+        <v>13.1389</v>
       </c>
       <c r="K11" t="n">
-        <v>-0.6080000000000001</v>
+        <v>7.3479</v>
       </c>
       <c r="L11" t="n">
-        <v>1.3839</v>
+        <v>5.791</v>
       </c>
       <c r="M11" t="n">
-        <v>-1.7598</v>
+        <v>-6.2559</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.4167999999999999</v>
+        <v>-4.762</v>
       </c>
       <c r="O11" t="n">
-        <v>-1.3429</v>
+        <v>-1.4939</v>
       </c>
       <c r="P11" t="n">
-        <v>-2.0811</v>
+        <v>-5.202800000000001</v>
       </c>
       <c r="Q11" t="n">
-        <v>-6.4517</v>
+        <v>-19.355</v>
       </c>
       <c r="R11" t="n">
-        <v>4.3705</v>
+        <v>14.1521</v>
       </c>
       <c r="S11" t="n">
-        <v>-3.9087</v>
+        <v>1.0161</v>
       </c>
       <c r="T11" t="n">
-        <v>-2.442</v>
+        <v>0.6513999999999999</v>
       </c>
       <c r="U11" t="n">
-        <v>-1.4664</v>
+        <v>0.3645999999999999</v>
       </c>
       <c r="V11" t="n">
-        <v>-1.3904</v>
+        <v>-11.2296</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>4.617</v>
       </c>
       <c r="X11" t="n">
-        <v>-1.3904</v>
+        <v>-15.8465</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>W. BURGOS CABRERA</t>
+          <t>A. GAYE</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1342,76 +1342,76 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="D12" t="n">
-        <v>-8.987699999999998</v>
+        <v>-8.649000000000001</v>
       </c>
       <c r="E12" t="n">
-        <v>-11.0955</v>
+        <v>-1.185</v>
       </c>
       <c r="F12" t="n">
-        <v>2.1077</v>
+        <v>-7.4639</v>
       </c>
       <c r="G12" t="n">
-        <v>-8.218</v>
+        <v>-8.405100000000001</v>
       </c>
       <c r="H12" t="n">
-        <v>-1.1917</v>
+        <v>-5.5182</v>
       </c>
       <c r="I12" t="n">
-        <v>-7.0261</v>
+        <v>-2.887</v>
       </c>
       <c r="J12" t="n">
-        <v>-8.0083</v>
+        <v>-2.9631</v>
       </c>
       <c r="K12" t="n">
-        <v>-1.917</v>
+        <v>-4.0604</v>
       </c>
       <c r="L12" t="n">
-        <v>-6.091500000000001</v>
+        <v>1.0973</v>
       </c>
       <c r="M12" t="n">
-        <v>-0.2093999999999998</v>
+        <v>-5.4419</v>
       </c>
       <c r="N12" t="n">
-        <v>0.7253999999999999</v>
+        <v>-1.4578</v>
       </c>
       <c r="O12" t="n">
-        <v>-0.9347</v>
+        <v>-3.9841</v>
       </c>
       <c r="P12" t="n">
-        <v>-2.775557561562891e-16</v>
+        <v>0.8324</v>
       </c>
       <c r="Q12" t="n">
-        <v>-10.6141</v>
+        <v>-2.0812</v>
       </c>
       <c r="R12" t="n">
-        <v>10.6141</v>
+        <v>2.9136</v>
       </c>
       <c r="S12" t="n">
-        <v>4.4593</v>
+        <v>0.1902</v>
       </c>
       <c r="T12" t="n">
-        <v>1.9549</v>
+        <v>0.1268</v>
       </c>
       <c r="U12" t="n">
-        <v>2.5045</v>
+        <v>0.06340000000000001</v>
       </c>
       <c r="V12" t="n">
-        <v>-5.2291</v>
+        <v>-1.2665</v>
       </c>
       <c r="W12" t="n">
-        <v>5.5724</v>
+        <v>3.7325</v>
       </c>
       <c r="X12" t="n">
-        <v>-10.8014</v>
+        <v>-4.999000000000001</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>P. FERNANDEZ CHOCARRO</t>
+          <t>J. KNOTEK</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1420,76 +1420,76 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="D13" t="n">
-        <v>-11.0772</v>
+        <v>-11.6526</v>
       </c>
       <c r="E13" t="n">
-        <v>7.0025</v>
+        <v>27.284</v>
       </c>
       <c r="F13" t="n">
-        <v>-18.0794</v>
+        <v>-38.9364</v>
       </c>
       <c r="G13" t="n">
-        <v>-1.633</v>
+        <v>-12.3629</v>
       </c>
       <c r="H13" t="n">
-        <v>-5.7305</v>
+        <v>-22.91</v>
       </c>
       <c r="I13" t="n">
-        <v>4.0977</v>
+        <v>10.5472</v>
       </c>
       <c r="J13" t="n">
-        <v>10.7233</v>
+        <v>37.9822</v>
       </c>
       <c r="K13" t="n">
-        <v>4.9315</v>
+        <v>9.412800000000001</v>
       </c>
       <c r="L13" t="n">
-        <v>5.7918</v>
+        <v>28.5693</v>
       </c>
       <c r="M13" t="n">
-        <v>-12.3558</v>
+        <v>-50.3449</v>
       </c>
       <c r="N13" t="n">
-        <v>-10.6618</v>
+        <v>-32.3227</v>
       </c>
       <c r="O13" t="n">
-        <v>-1.694</v>
+        <v>-18.0221</v>
       </c>
       <c r="P13" t="n">
-        <v>11.4465</v>
+        <v>-1.665</v>
       </c>
       <c r="Q13" t="n">
-        <v>-9.989699999999999</v>
+        <v>-45.7862</v>
       </c>
       <c r="R13" t="n">
-        <v>21.4361</v>
+        <v>44.121</v>
       </c>
       <c r="S13" t="n">
-        <v>-11.2854</v>
+        <v>-16.0364</v>
       </c>
       <c r="T13" t="n">
-        <v>-2.0099</v>
+        <v>-7.5448</v>
       </c>
       <c r="U13" t="n">
-        <v>-9.275499999999999</v>
+        <v>-8.4916</v>
       </c>
       <c r="V13" t="n">
-        <v>-9.605699999999999</v>
+        <v>18.4114</v>
       </c>
       <c r="W13" t="n">
-        <v>8.279</v>
+        <v>42.6324</v>
       </c>
       <c r="X13" t="n">
-        <v>-17.8845</v>
+        <v>-24.2209</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>J. KNOTEK</t>
+          <t>W. BURGOS CABRERA</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1498,70 +1498,70 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>25</v>
+        <v>11</v>
       </c>
       <c r="D14" t="n">
-        <v>-21.2503</v>
+        <v>-13.608</v>
       </c>
       <c r="E14" t="n">
-        <v>17.9796</v>
+        <v>-14.4591</v>
       </c>
       <c r="F14" t="n">
-        <v>-39.2297</v>
+        <v>0.8512</v>
       </c>
       <c r="G14" t="n">
-        <v>-12.3629</v>
+        <v>-8.218</v>
       </c>
       <c r="H14" t="n">
-        <v>-22.91</v>
+        <v>-1.1917</v>
       </c>
       <c r="I14" t="n">
-        <v>10.5472</v>
+        <v>-7.0261</v>
       </c>
       <c r="J14" t="n">
-        <v>37.9822</v>
+        <v>-8.0083</v>
       </c>
       <c r="K14" t="n">
-        <v>9.412800000000001</v>
+        <v>-1.917</v>
       </c>
       <c r="L14" t="n">
-        <v>28.5693</v>
+        <v>-6.091500000000001</v>
       </c>
       <c r="M14" t="n">
-        <v>-50.3449</v>
+        <v>-0.2093999999999998</v>
       </c>
       <c r="N14" t="n">
-        <v>-32.3227</v>
+        <v>0.7253999999999999</v>
       </c>
       <c r="O14" t="n">
-        <v>-18.0221</v>
+        <v>-0.9347</v>
       </c>
       <c r="P14" t="n">
-        <v>-1.665</v>
+        <v>-2.775557561562891e-16</v>
       </c>
       <c r="Q14" t="n">
-        <v>-45.7862</v>
+        <v>-10.6141</v>
       </c>
       <c r="R14" t="n">
-        <v>44.121</v>
+        <v>10.6141</v>
       </c>
       <c r="S14" t="n">
-        <v>-25.6341</v>
+        <v>-0.1609999999999999</v>
       </c>
       <c r="T14" t="n">
-        <v>-16.8491</v>
+        <v>-1.4089</v>
       </c>
       <c r="U14" t="n">
-        <v>-8.785</v>
+        <v>1.2478</v>
       </c>
       <c r="V14" t="n">
-        <v>18.4114</v>
+        <v>-5.2291</v>
       </c>
       <c r="W14" t="n">
-        <v>42.6324</v>
+        <v>5.5724</v>
       </c>
       <c r="X14" t="n">
-        <v>-24.2209</v>
+        <v>-10.8014</v>
       </c>
     </row>
     <row r="15">
@@ -1579,13 +1579,13 @@
         <v>13</v>
       </c>
       <c r="D15" t="n">
-        <v>-26.6286</v>
+        <v>-16.3131</v>
       </c>
       <c r="E15" t="n">
-        <v>-12.7297</v>
+        <v>-6.4168</v>
       </c>
       <c r="F15" t="n">
-        <v>-13.8989</v>
+        <v>-9.896100000000001</v>
       </c>
       <c r="G15" t="n">
         <v>-3.5447</v>
@@ -1624,13 +1624,13 @@
         <v>23.7254</v>
       </c>
       <c r="S15" t="n">
-        <v>-20.1179</v>
+        <v>-9.8019</v>
       </c>
       <c r="T15" t="n">
-        <v>-12.208</v>
+        <v>-5.8947</v>
       </c>
       <c r="U15" t="n">
-        <v>-7.9098</v>
+        <v>-3.9073</v>
       </c>
       <c r="V15" t="n">
         <v>-1.0931</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>J. DJERY</t>
+          <t>A. RUBIERA RAPOSO</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1654,76 +1654,76 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="D16" t="n">
-        <v>-29.6183</v>
+        <v>-30.277</v>
       </c>
       <c r="E16" t="n">
-        <v>-16.0811</v>
+        <v>-20.2412</v>
       </c>
       <c r="F16" t="n">
-        <v>-13.5369</v>
+        <v>-10.0355</v>
       </c>
       <c r="G16" t="n">
-        <v>-17.9669</v>
+        <v>-27.3075</v>
       </c>
       <c r="H16" t="n">
-        <v>-11.0609</v>
+        <v>-16.738</v>
       </c>
       <c r="I16" t="n">
-        <v>-6.906099999999999</v>
+        <v>-10.5695</v>
       </c>
       <c r="J16" t="n">
-        <v>1.2996</v>
+        <v>-9.992100000000001</v>
       </c>
       <c r="K16" t="n">
-        <v>-1.9139</v>
+        <v>-3.868</v>
       </c>
       <c r="L16" t="n">
-        <v>3.2135</v>
+        <v>-6.124099999999999</v>
       </c>
       <c r="M16" t="n">
-        <v>-19.2663</v>
+        <v>-17.315</v>
       </c>
       <c r="N16" t="n">
-        <v>-9.146800000000001</v>
+        <v>-12.8701</v>
       </c>
       <c r="O16" t="n">
-        <v>-10.1193</v>
+        <v>-4.4453</v>
       </c>
       <c r="P16" t="n">
-        <v>-14.5684</v>
+        <v>4.1623</v>
       </c>
       <c r="Q16" t="n">
-        <v>-28.9284</v>
+        <v>-13.7359</v>
       </c>
       <c r="R16" t="n">
-        <v>14.3602</v>
+        <v>17.8981</v>
       </c>
       <c r="S16" t="n">
-        <v>9.7028</v>
+        <v>-4.4959</v>
       </c>
       <c r="T16" t="n">
-        <v>7.355099999999999</v>
+        <v>-0.4582000000000001</v>
       </c>
       <c r="U16" t="n">
-        <v>2.3475</v>
+        <v>-4.0378</v>
       </c>
       <c r="V16" t="n">
-        <v>-6.7857</v>
+        <v>-2.6357</v>
       </c>
       <c r="W16" t="n">
-        <v>4.1925</v>
+        <v>3.9449</v>
       </c>
       <c r="X16" t="n">
-        <v>-10.9783</v>
+        <v>-6.5806</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>P. YARNOZ LUMBRERAS</t>
+          <t>J. POTIER</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1732,76 +1732,76 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D17" t="n">
-        <v>-31.3156</v>
+        <v>-34.8717</v>
       </c>
       <c r="E17" t="n">
-        <v>-10.8603</v>
+        <v>-7.765400000000001</v>
       </c>
       <c r="F17" t="n">
-        <v>-20.4549</v>
+        <v>-27.1063</v>
       </c>
       <c r="G17" t="n">
-        <v>-33.2812</v>
+        <v>28.3688</v>
       </c>
       <c r="H17" t="n">
-        <v>-23.5174</v>
+        <v>8.944700000000001</v>
       </c>
       <c r="I17" t="n">
-        <v>-9.7636</v>
+        <v>19.4239</v>
       </c>
       <c r="J17" t="n">
-        <v>7.588200000000001</v>
+        <v>62.2532</v>
       </c>
       <c r="K17" t="n">
-        <v>0.7584999999999997</v>
+        <v>30.64</v>
       </c>
       <c r="L17" t="n">
-        <v>6.83</v>
+        <v>31.6129</v>
       </c>
       <c r="M17" t="n">
-        <v>-40.8699</v>
+        <v>-33.8845</v>
       </c>
       <c r="N17" t="n">
-        <v>-24.2764</v>
+        <v>-21.6955</v>
       </c>
       <c r="O17" t="n">
-        <v>-16.5934</v>
+        <v>-12.1887</v>
       </c>
       <c r="P17" t="n">
-        <v>4.786799999999999</v>
+        <v>-44.9536</v>
       </c>
       <c r="Q17" t="n">
-        <v>-45.578</v>
+        <v>-86.5774</v>
       </c>
       <c r="R17" t="n">
-        <v>50.3646</v>
+        <v>41.6237</v>
       </c>
       <c r="S17" t="n">
-        <v>1.3358</v>
+        <v>-16.1928</v>
       </c>
       <c r="T17" t="n">
-        <v>8.5015</v>
+        <v>-5.571400000000001</v>
       </c>
       <c r="U17" t="n">
-        <v>-7.1655</v>
+        <v>-10.6209</v>
       </c>
       <c r="V17" t="n">
-        <v>-4.157</v>
+        <v>-2.094399999999999</v>
       </c>
       <c r="W17" t="n">
-        <v>18.6276</v>
+        <v>22.1299</v>
       </c>
       <c r="X17" t="n">
-        <v>-22.7843</v>
+        <v>-24.2245</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A. RUBIERA RAPOSO</t>
+          <t>J. DJERY</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1810,76 +1810,76 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="D18" t="n">
-        <v>-36.2928</v>
+        <v>-37.7141</v>
       </c>
       <c r="E18" t="n">
-        <v>-24.0199</v>
+        <v>-21.3642</v>
       </c>
       <c r="F18" t="n">
-        <v>-12.2727</v>
+        <v>-16.3498</v>
       </c>
       <c r="G18" t="n">
-        <v>-27.3075</v>
+        <v>-17.9669</v>
       </c>
       <c r="H18" t="n">
-        <v>-16.738</v>
+        <v>-11.0609</v>
       </c>
       <c r="I18" t="n">
-        <v>-10.5695</v>
+        <v>-6.906099999999999</v>
       </c>
       <c r="J18" t="n">
-        <v>-9.992100000000001</v>
+        <v>1.2996</v>
       </c>
       <c r="K18" t="n">
-        <v>-3.868</v>
+        <v>-1.9139</v>
       </c>
       <c r="L18" t="n">
-        <v>-6.124099999999999</v>
+        <v>3.2135</v>
       </c>
       <c r="M18" t="n">
-        <v>-17.315</v>
+        <v>-19.2663</v>
       </c>
       <c r="N18" t="n">
-        <v>-12.8701</v>
+        <v>-9.146800000000001</v>
       </c>
       <c r="O18" t="n">
-        <v>-4.4453</v>
+        <v>-10.1193</v>
       </c>
       <c r="P18" t="n">
-        <v>4.1623</v>
+        <v>-14.5684</v>
       </c>
       <c r="Q18" t="n">
-        <v>-13.7359</v>
+        <v>-28.9284</v>
       </c>
       <c r="R18" t="n">
-        <v>17.8981</v>
+        <v>14.3602</v>
       </c>
       <c r="S18" t="n">
-        <v>-10.5117</v>
+        <v>1.6069</v>
       </c>
       <c r="T18" t="n">
-        <v>-4.2367</v>
+        <v>2.0722</v>
       </c>
       <c r="U18" t="n">
-        <v>-6.2749</v>
+        <v>-0.4654</v>
       </c>
       <c r="V18" t="n">
-        <v>-2.6357</v>
+        <v>-6.7857</v>
       </c>
       <c r="W18" t="n">
-        <v>3.9449</v>
+        <v>4.1925</v>
       </c>
       <c r="X18" t="n">
-        <v>-6.5806</v>
+        <v>-10.9783</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>J. POTIER</t>
+          <t>P. YARNOZ LUMBRERAS</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1888,76 +1888,76 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D19" t="n">
-        <v>-49.7685</v>
+        <v>-39.2713</v>
       </c>
       <c r="E19" t="n">
-        <v>-19.6322</v>
+        <v>-19.0041</v>
       </c>
       <c r="F19" t="n">
-        <v>-30.136</v>
+        <v>-20.2673</v>
       </c>
       <c r="G19" t="n">
-        <v>28.3688</v>
+        <v>-33.2812</v>
       </c>
       <c r="H19" t="n">
-        <v>8.944700000000001</v>
+        <v>-23.5174</v>
       </c>
       <c r="I19" t="n">
-        <v>19.4239</v>
+        <v>-9.7636</v>
       </c>
       <c r="J19" t="n">
-        <v>62.2532</v>
+        <v>7.588200000000001</v>
       </c>
       <c r="K19" t="n">
-        <v>30.64</v>
+        <v>0.7584999999999997</v>
       </c>
       <c r="L19" t="n">
-        <v>31.6129</v>
+        <v>6.83</v>
       </c>
       <c r="M19" t="n">
-        <v>-33.8845</v>
+        <v>-40.8699</v>
       </c>
       <c r="N19" t="n">
-        <v>-21.6955</v>
+        <v>-24.2764</v>
       </c>
       <c r="O19" t="n">
-        <v>-12.1887</v>
+        <v>-16.5934</v>
       </c>
       <c r="P19" t="n">
-        <v>-44.9536</v>
+        <v>4.786799999999999</v>
       </c>
       <c r="Q19" t="n">
-        <v>-86.5774</v>
+        <v>-45.578</v>
       </c>
       <c r="R19" t="n">
-        <v>41.6237</v>
+        <v>50.3646</v>
       </c>
       <c r="S19" t="n">
-        <v>-31.0891</v>
+        <v>-6.6198</v>
       </c>
       <c r="T19" t="n">
-        <v>-17.4381</v>
+        <v>0.3582</v>
       </c>
       <c r="U19" t="n">
-        <v>-13.651</v>
+        <v>-6.9775</v>
       </c>
       <c r="V19" t="n">
-        <v>-2.094399999999999</v>
+        <v>-4.157</v>
       </c>
       <c r="W19" t="n">
-        <v>22.1299</v>
+        <v>18.6276</v>
       </c>
       <c r="X19" t="n">
-        <v>-24.2245</v>
+        <v>-22.7843</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>J. LACUNZA ABECIA</t>
+          <t>A. CALVO TORRES</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1966,76 +1966,76 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="D20" t="n">
-        <v>-56.4895</v>
+        <v>-48.4437</v>
       </c>
       <c r="E20" t="n">
-        <v>-22.7557</v>
+        <v>-21.3442</v>
       </c>
       <c r="F20" t="n">
-        <v>-33.7337</v>
+        <v>-27.0997</v>
       </c>
       <c r="G20" t="n">
-        <v>-45.7186</v>
+        <v>-1.4858</v>
       </c>
       <c r="H20" t="n">
-        <v>-20.1834</v>
+        <v>-4.856199999999999</v>
       </c>
       <c r="I20" t="n">
-        <v>-25.5352</v>
+        <v>3.37</v>
       </c>
       <c r="J20" t="n">
-        <v>-6.5898</v>
+        <v>26.27</v>
       </c>
       <c r="K20" t="n">
-        <v>2.8912</v>
+        <v>8.9887</v>
       </c>
       <c r="L20" t="n">
-        <v>-9.480499999999999</v>
+        <v>17.2815</v>
       </c>
       <c r="M20" t="n">
-        <v>-39.1292</v>
+        <v>-27.7558</v>
       </c>
       <c r="N20" t="n">
-        <v>-23.0747</v>
+        <v>-13.8442</v>
       </c>
       <c r="O20" t="n">
-        <v>-16.0546</v>
+        <v>-13.9115</v>
       </c>
       <c r="P20" t="n">
-        <v>2.705500000000001</v>
+        <v>-23.1013</v>
       </c>
       <c r="Q20" t="n">
-        <v>-31.0098</v>
+        <v>-58.2734</v>
       </c>
       <c r="R20" t="n">
-        <v>33.7151</v>
+        <v>35.1719</v>
       </c>
       <c r="S20" t="n">
-        <v>-6.5135</v>
+        <v>-12.8749</v>
       </c>
       <c r="T20" t="n">
-        <v>1.9477</v>
+        <v>-5.8811</v>
       </c>
       <c r="U20" t="n">
-        <v>-8.4612</v>
+        <v>-6.9938</v>
       </c>
       <c r="V20" t="n">
-        <v>-6.962700000000001</v>
+        <v>-10.9818</v>
       </c>
       <c r="W20" t="n">
-        <v>12.896</v>
+        <v>16.54</v>
       </c>
       <c r="X20" t="n">
-        <v>-19.8585</v>
+        <v>-27.522</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A. CALVO TORRES</t>
+          <t>J. LACUNZA ABECIA</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2044,70 +2044,70 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="D21" t="n">
-        <v>-61.3554</v>
+        <v>-58.0507</v>
       </c>
       <c r="E21" t="n">
-        <v>-30.2104</v>
+        <v>-24.7125</v>
       </c>
       <c r="F21" t="n">
-        <v>-31.1449</v>
+        <v>-33.3384</v>
       </c>
       <c r="G21" t="n">
-        <v>-1.4858</v>
+        <v>-45.7186</v>
       </c>
       <c r="H21" t="n">
-        <v>-4.856199999999999</v>
+        <v>-20.1834</v>
       </c>
       <c r="I21" t="n">
-        <v>3.37</v>
+        <v>-25.5352</v>
       </c>
       <c r="J21" t="n">
-        <v>26.27</v>
+        <v>-6.5898</v>
       </c>
       <c r="K21" t="n">
-        <v>8.9887</v>
+        <v>2.8912</v>
       </c>
       <c r="L21" t="n">
-        <v>17.2815</v>
+        <v>-9.480499999999999</v>
       </c>
       <c r="M21" t="n">
-        <v>-27.7558</v>
+        <v>-39.1292</v>
       </c>
       <c r="N21" t="n">
-        <v>-13.8442</v>
+        <v>-23.0747</v>
       </c>
       <c r="O21" t="n">
-        <v>-13.9115</v>
+        <v>-16.0546</v>
       </c>
       <c r="P21" t="n">
-        <v>-23.1013</v>
+        <v>2.705500000000001</v>
       </c>
       <c r="Q21" t="n">
-        <v>-58.2734</v>
+        <v>-31.0098</v>
       </c>
       <c r="R21" t="n">
-        <v>35.1719</v>
+        <v>33.7151</v>
       </c>
       <c r="S21" t="n">
-        <v>-25.7872</v>
+        <v>-8.0749</v>
       </c>
       <c r="T21" t="n">
-        <v>-14.7475</v>
+        <v>-0.009199999999999819</v>
       </c>
       <c r="U21" t="n">
-        <v>-11.0397</v>
+        <v>-8.065799999999999</v>
       </c>
       <c r="V21" t="n">
-        <v>-10.9818</v>
+        <v>-6.962700000000001</v>
       </c>
       <c r="W21" t="n">
-        <v>16.54</v>
+        <v>12.896</v>
       </c>
       <c r="X21" t="n">
-        <v>-27.522</v>
+        <v>-19.8585</v>
       </c>
     </row>
     <row r="22">
@@ -2125,13 +2125,13 @@
         <v>26</v>
       </c>
       <c r="D22" t="n">
-        <v>-338.811</v>
+        <v>-315.5135</v>
       </c>
       <c r="E22" t="n">
-        <v>-114.4351</v>
+        <v>-103.9971</v>
       </c>
       <c r="F22" t="n">
-        <v>-224.3743</v>
+        <v>-211.5169</v>
       </c>
       <c r="G22" t="n">
         <v>-128.4738</v>
@@ -2146,7 +2146,7 @@
         <v>178.8656</v>
       </c>
       <c r="K22" t="n">
-        <v>84.93940000000001</v>
+        <v>84.93939999999999</v>
       </c>
       <c r="L22" t="n">
         <v>93.9271</v>
@@ -2167,16 +2167,16 @@
         <v>-412.0756999999999</v>
       </c>
       <c r="R22" t="n">
-        <v>349.6386</v>
+        <v>349.6385999999999</v>
       </c>
       <c r="S22" t="n">
-        <v>-104.5097</v>
+        <v>-81.21169999999999</v>
       </c>
       <c r="T22" t="n">
-        <v>-36.7913</v>
+        <v>-26.3525</v>
       </c>
       <c r="U22" t="n">
-        <v>-67.7171</v>
+        <v>-54.8583</v>
       </c>
       <c r="V22" t="n">
         <v>-43.3928</v>
